--- a/AI Audit Log_NguyenThiLeQuyen.xlsx
+++ b/AI Audit Log_NguyenThiLeQuyen.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="5" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 1" sheetId="5" r:id="rId2"/>
+    <sheet name="Week 2" sheetId="6" r:id="rId3"/>
+    <sheet name="Assignment 2" sheetId="3" r:id="rId4"/>
+    <sheet name="Assignment 3" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>STT</t>
   </si>
@@ -119,6 +120,37 @@
   <si>
     <t>Phản hồi: AI liệt kê: Requirement -&gt; Design -&gt; Coding -&gt; Testing -&gt; Deployment.
 Kiểm chứng: Tôi nhận thấy bước 'Testing' trong phản hồi của AI hơi chung chung. Tôi đã yêu cầu AI làm rõ quy trình kiểm thử đơn vị (Unit Test) để bổ sung vào kế hoạch triển khai của mình.</t>
+  </si>
+  <si>
+    <t>"Tôi đang làm hệ thống liên quan đến bán hàng. Dựa vào yêu cầu hệ thống, Ai hoặc những hệ thống nào sẽ tương tác trực tiếp với phần mềm này để thực hiện công việc? Hãy phân loại giúp tôi đâu là Actor chính (Primary) và Actor phụ (Secondary)."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê ra các nhóm người dùng con người và các hệ thống bên thứ ba tương tác với hệ thống (như Cổng thanh toán, Timer hệ thống).
+Quyết định: Tôi nhận thấy AI đưa cả "Hệ thống Cơ sở dữ liệu (Database)" vào làm Actor. Dựa trên kiến thức học, DB là thành phần nội bộ (Hộp đen) chứ không phải tác nhân bên ngoài. Tôi quyết định lọc bỏ Database ra khỏi danh sách Actor để chuẩn hóa biểu đồ.</t>
+  </si>
+  <si>
+    <t>"Với các Actor đã xác định ở trên, hệ thống làm được gì để mang lại giá trị trọn vẹn cho họ? Hãy liệt kê các Use Case chính theo cấu trúc tên dạng: Động từ + Tác từ và tránh phân rã quá vụn vặt."</t>
+  </si>
+  <si>
+    <t>Phản hồi:AI đề xuất danh sách các Use Case như: Đăng nhập, Tìm kiếm sản phẩm, Xem giỏ hàng, Nhấp nút đặt hàng, Thanh toán hóa đơn.
+Kiểm chứng:Tôi nhận thấy các hành động như "Xem giỏ hàng", "Nhấp nút đặt hàng" bị sa đà vào thiết kế giao diện (UI/UX) và phân rã chức năng quá nhỏ, chưa tạo ra giá trị độc lập. Tôi quyết định tối ưu bằng cách gom chúng lại thành một Use Case lớn có ý nghĩa là "Đặt hàng".</t>
+  </si>
+  <si>
+    <t>"Giữa các Use Case và Actor vừa chọn, chúng kết nối với nhau như thế nào? Khi nào thì tôi nên dùng mối quan hệ &lt;&lt;include&gt;&gt; (bắt buộc), &lt;&lt;extend&gt;&gt; (tùy chọn) và Generalization (kế thừa) để biểu đồ chuẩn logic?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: Dùng &lt;&lt;include&gt;&gt; khi hành động phía sau luôn luôn phải chạy ; dùng &lt;&lt;extend&gt;&gt; cho các kịch bản rẽ nhánh, tùy chọn hoặc luồng ngoại lệ xảy ra theo điều kiện.
+Kiểm chứng: Tôi rà soát lại và thấy AI gợi ý vẽ đường &lt;&lt;include&gt;&gt; từ mọi Use Case đến ô "Đăng nhập". Điều này làm biểu đồ bị rối như mạng nhện. Tôi quyết định tối ưu bằng cách chuyển 'Đăng nhập' thành Điều kiện tiên quyết (Precondition) trong tài liệu đặc tả, giúp biểu đồ thoáng và sạch hơn.</t>
+  </si>
+  <si>
+    <t>Algorithm Design</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để viết tài liệu đặc tả (Use Case Specification) và vẽ Activity Diagram hoàn chỉnh cho Use Case '[Chọn 1 Use Case quan trọng, ví dụ: Đặt hàng]' bao gồm cả luồng chính suôn sẻ và các luồng ngoại lệ khi gặp lỗi?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI cung cấp cấu trúc kịch bản chuẩn (gồm Summary, Precondition, Main sequence, Alternative sequence, Postcondition) và phác thảo các bước rẽ nhánh cho sơ đồ hoạt động.
+Kiểm chứng: Tôi phát hiện luồng xử lý của AI chưa có bước giải quyết khi "Khách hàng bị từ chối thẻ tín dụng" hoặc "Hết hàng trong kho". Tôi đã chủ động bổ sung thêm các Luồng thay thế (Alternative Flows) này vào tài liệu đặc tả của mình để đảm bảo tính đầy đủ và có thể kiểm chứng của yêu cầu phần mềm.  </t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1177,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" ht="69" spans="1:5">
+    <row r="2" ht="55.2" spans="1:5">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1187,7 +1219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="82.8" spans="1:5">
+    <row r="5" ht="69" spans="1:5">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1299,9 +1331,87 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
-  <sheetData/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
+    <col min="2" max="2" width="33.4" customWidth="1"/>
+    <col min="3" max="3" width="31.6" customWidth="1"/>
+    <col min="4" max="4" width="53.2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="124.2" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" ht="124.2" spans="1:5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" ht="124.2" spans="1:5">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="138" spans="1:5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1316,4 +1426,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/AI Audit Log_NguyenThiLeQuyen.xlsx
+++ b/AI Audit Log_NguyenThiLeQuyen.xlsx
@@ -4,14 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="8400" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week 1" sheetId="5" r:id="rId2"/>
     <sheet name="Week 2" sheetId="6" r:id="rId3"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId4"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId5"/>
+    <sheet name="Week 3" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>STT</t>
   </si>
@@ -151,6 +150,72 @@
   <si>
     <t xml:space="preserve">Phản hồi: AI cung cấp cấu trúc kịch bản chuẩn (gồm Summary, Precondition, Main sequence, Alternative sequence, Postcondition) và phác thảo các bước rẽ nhánh cho sơ đồ hoạt động.
 Kiểm chứng: Tôi phát hiện luồng xử lý của AI chưa có bước giải quyết khi "Khách hàng bị từ chối thẻ tín dụng" hoặc "Hết hàng trong kho". Tôi đã chủ động bổ sung thêm các Luồng thay thế (Alternative Flows) này vào tài liệu đặc tả của mình để đảm bảo tính đầy đủ và có thể kiểm chứng của yêu cầu phần mềm.  </t>
+  </si>
+  <si>
+    <t>"Tôi đã thiết kế Class Diagram cho hệ thống AutoGo Car Rental. Hãy đề xuất các lớp chính và mối quan hệ giữa chúng."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các lớp User, Customer, Staff, Car, Booking và Payment. AI cũng đề xuất Customer và Staff kế thừa User.
+Quyết định: Kết quả phù hợp với sơ đồ tôi đã xây dựng nên tôi giữ nguyên mô hình kế thừa này.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra các quan hệ UML trong hệ thống thuê xe có hợp lý không."</t>
+  </si>
+  <si>
+    <t>Phản hồi:AI đề xuất Association giữa Customer–Booking, Booking–Car và Composition giữa Booking–Payment.
+Kiểm chứng:Tôi nhận thấy quan hệ Booking–Payment nên dùng Composition vì Payment không tồn tại độc lập khi Booking bị xóa. Tôi điều chỉnh sơ đồ theo đề xuất này.</t>
+  </si>
+  <si>
+    <t>"Áp dụng Repository Pattern cho hệ thống AutoGo như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất IRepository, UserRepository, BookingRepository, CarRepository và PaymentRepository.
+Kiểm chứng: Ban đầu sơ đồ của tôi chỉ có Repository chung. Sau khi tham khảo AI, tôi bổ sung các Repository chuyên biệt để thể hiện rõ dữ liệu của từng đối tượng.</t>
+  </si>
+  <si>
+    <t>Algorithm / Architecture</t>
+  </si>
+  <si>
+    <t>"Business logic thanh toán nên đặt ở đâu trong Layered Architecture?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất PaymentService xử lý nghiệp vụ thanh toán và phụ thuộc vào PaymentRepository
+Kiểm chứng: Tôi đồng ý với đề xuất này vì phù hợp với yêu cầu đề bài và nguyên tắc tách biệt business logic khỏi data access.</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>"Các phương thức login() và logout() 
+có nên đặt trong lớp User không?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI ban đầu đề xuất login() và logout() trong lớp User. 
+Kiểm chứng: Tôi nhận thấy điều này chưa phù hợp với Layered 
+Architecture vì đây là nghiệp vụ xác thực. Tôi chuyển các chức 
+năng này sang Service Layer và chỉ giữ dữ liệu người dùng trong lớp User.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra Class Diagram đã đáp ứng 
+đầy đủ yêu cầu đề bài chưa."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận sơ đồ đã có Inheritance, Interface 
+Implementation, Association, Composition và Dependency.
+Kiểm chứng: Tôi đối chiếu lại đề bài và nhận thấy tất cả yêu cầu 
+bắt buộc đã được đáp ứng.</t>
+  </si>
+  <si>
+    <t>Reflection</t>
+  </si>
+  <si>
+    <t>"So sánh thiết kế của tôi với thiết kế 
+do AI đề xuất."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất nhiều phương thức và interface hơn so với 
+sơ đồ ban đầu của tôi.
+Quyết định: Tôi giữ lại các thành phần quan trọng như PaymentService và IRepository, đồng thời lược bỏ một số phương thức không cần thiết để sơ đồ rõ ràng và phù hợp phạm vi bài tập hơn.</t>
   </si>
 </sst>
 </file>
@@ -794,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,6 +876,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1420,20 +1489,129 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
-  <sheetData/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
+    <col min="2" max="2" width="33.4" customWidth="1"/>
+    <col min="3" max="3" width="31.6" customWidth="1"/>
+    <col min="4" max="4" width="53.2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="69" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" ht="82.8" spans="1:5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" ht="82.8" spans="1:5">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="69" spans="1:5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="82.8" spans="1:5">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" ht="69" spans="1:5">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="96.6" spans="1:5">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
